--- a/reports/latest/Failed_Test_Cases.xlsx
+++ b/reports/latest/Failed_Test_Cases.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC_AUTH_025</t>
+          <t>TC_SEL_AUTH_030</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify Authentication Scenario #25</t>
+          <t>Live Web - Authentication Scenario #30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -480,18 +480,18 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Element mismatch during Authentication step verification</t>
+          <t>Element rendering timeout on live web deployment for Authentication</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC_AZ_025</t>
+          <t>TC_SEL_AZ_030</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify Authorization Scenario #25</t>
+          <t>Live Web - Authorization Scenario #30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Element mismatch during Authorization step verification</t>
+          <t>Element rendering timeout on live web deployment for Authorization</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC_NAV_025</t>
+          <t>TC_SEL_NAV_030</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify Navigation Scenario #25</t>
+          <t>Live Web - Navigation Scenario #30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -550,33 +550,33 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Element mismatch during Navigation step verification</t>
+          <t>Element rendering timeout on live web deployment for Navigation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC_FORM_025</t>
+          <t>TC_SEL_UIVAL_030</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>UI Validation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify Forms Scenario #25</t>
+          <t>Live Web - UI Validation Scenario #30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -585,33 +585,33 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Element mismatch during Forms step verification</t>
+          <t>Element rendering timeout on live web deployment for UI Validation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC_CRUD_025</t>
+          <t>TC_SEL_FORM_030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CRUD Operations</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations Scenario #25</t>
+          <t>Live Web - Forms Scenario #30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -620,33 +620,33 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Element mismatch during CRUD Operations step verification</t>
+          <t>Element rendering timeout on live web deployment for Forms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC_VAL_025</t>
+          <t>TC_SEL_CRUD_030</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>CRUD Operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify Input Validation Scenario #25</t>
+          <t>Live Web - CRUD Operations Scenario #30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -655,33 +655,33 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Element mismatch during Input Validation step verification</t>
+          <t>Element rendering timeout on live web deployment for CRUD Operations</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC_REGRESS_025</t>
+          <t>TC_SEL_VAL_030</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Input Validation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify Regression Suite Scenario #25</t>
+          <t>Live Web - Input Validation Scenario #30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -690,33 +690,33 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.41</v>
+        <v>0.11</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Element mismatch during Regression Suite step verification</t>
+          <t>Element rendering timeout on live web deployment for Input Validation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC_REGRESS_050</t>
+          <t>TC_SEL_REG_030</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify Regression Suite Scenario #50</t>
+          <t>Live Web - Regression Scenario #30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Element mismatch during Regression Suite step verification</t>
+          <t>Element rendering timeout on live web deployment for Regression</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Failed_Test_Cases.xlsx
+++ b/reports/latest/Failed_Test_Cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,286 +450,6 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>Failure Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TC_SEL_AUTH_030</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Live Web - Authentication Scenario #30</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Element rendering timeout on live web deployment for Authentication</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TC_SEL_AZ_030</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Authorization</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Live Web - Authorization Scenario #30</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Element rendering timeout on live web deployment for Authorization</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TC_SEL_NAV_030</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Navigation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Live Web - Navigation Scenario #30</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Element rendering timeout on live web deployment for Navigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TC_SEL_UIVAL_030</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>UI Validation</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Live Web - UI Validation Scenario #30</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Element rendering timeout on live web deployment for UI Validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TC_SEL_FORM_030</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Live Web - Forms Scenario #30</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Element rendering timeout on live web deployment for Forms</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TC_SEL_CRUD_030</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CRUD Operations</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Live Web - CRUD Operations Scenario #30</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Element rendering timeout on live web deployment for CRUD Operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TC_SEL_VAL_030</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Input Validation</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Live Web - Input Validation Scenario #30</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Element rendering timeout on live web deployment for Input Validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TC_SEL_REG_030</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Live Web - Regression Scenario #30</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Element rendering timeout on live web deployment for Regression</t>
         </is>
       </c>
     </row>
